--- a/Tkb_luu_last/tkb_chung.xlsx
+++ b/Tkb_luu_last/tkb_chung.xlsx
@@ -419,102 +419,102 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Thứ</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Tiet</t>
+          <t>Tiết</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Lop_6A1</t>
+          <t>6A1</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Lop_6A2</t>
+          <t>6A2</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Lop_7A1</t>
+          <t>7A1</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Lop_8A1</t>
+          <t>8A1</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Lop_8A2</t>
+          <t>8A2</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Lop_9A1</t>
+          <t>9A1</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Lop_9A2</t>
+          <t>9A2</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Lop_9A3</t>
+          <t>9A3</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Lop_10A1</t>
+          <t>10A1</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Lop_10A2</t>
+          <t>10A2</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Lop_10A3</t>
+          <t>10A3</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Lop_10A4</t>
+          <t>10A4</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Lop_11A1</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Lop_11A2</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Lop_11A3</t>
+          <t>11A3</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Lop_12A1</t>
+          <t>12A1</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Lop_12A2</t>
+          <t>12A2</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Lop_12A3</t>
+          <t>12A3</t>
         </is>
       </c>
     </row>
@@ -527,13 +527,13 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Thư_AV</t>
+          <t>Việt_CC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Như_AV</t>
+          <t>Phúc_CC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -883,13 +883,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Việt_CC</t>
+          <t>Thư_AV</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Phúc_CC</t>
+          <t>Như_AV</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
